--- a/data/trans_dic/P39A3_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P39A3_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 93,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,43; 94,9</t>
+          <t>85,69; 95,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,51; 95,88</t>
+          <t>88,22; 96,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,48; 94,67</t>
+          <t>88,45; 94,57</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,48; 95,5</t>
+          <t>88,27; 95,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,89; 92,6</t>
+          <t>43,63; 92,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,03; 92,93</t>
+          <t>64,41; 93,02</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,95; 93,81</t>
+          <t>89,04; 93,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,32; 92,28</t>
+          <t>88,02; 92,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,44; 92,47</t>
+          <t>89,34; 92,55</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,95; 98,12</t>
+          <t>92,14; 97,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,91; 91,65</t>
+          <t>87,89; 91,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,83; 95,91</t>
+          <t>90,84; 95,63</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,55; 93,02</t>
+          <t>88,58; 93,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,28; 93,46</t>
+          <t>90,07; 93,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,08; 92,94</t>
+          <t>89,89; 92,77</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>87,74; 92,7</t>
+          <t>87,69; 92,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,96; 98,22</t>
+          <t>90,94; 98,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90,41; 96,63</t>
+          <t>90,49; 96,54</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>84,55; 91,01</t>
+          <t>84,28; 91,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83,76; 89,02</t>
+          <t>83,94; 89,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85,13; 89,25</t>
+          <t>85,3; 89,14</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>90,76; 93,69</t>
+          <t>90,85; 94,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>82,69; 91,78</t>
+          <t>82,87; 91,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87,25; 92,12</t>
+          <t>86,62; 92,13</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 93,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>308251; 342432</t>
+          <t>309200; 343136</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>243346; 266625</t>
+          <t>245314; 267376</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>565337; 604883</t>
+          <t>565110; 604233</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>348207; 375840</t>
+          <t>347383; 375730</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>225019; 454015</t>
+          <t>213946; 455174</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>565960; 821351</t>
+          <t>569305; 822133</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>461993; 487260</t>
+          <t>462457; 487513</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>464080; 484903</t>
+          <t>462533; 484052</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>934493; 966189</t>
+          <t>933537; 967004</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>791291; 844338</t>
+          <t>792853; 842148</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>580002; 604679</t>
+          <t>579876; 603769</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1380889; 1458020</t>
+          <t>1381031; 1453828</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>472675; 496527</t>
+          <t>472832; 496927</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475055; 491810</t>
+          <t>473978; 492321</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>954806; 985105</t>
+          <t>952813; 983347</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>299384; 316297</t>
+          <t>299197; 316869</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>526888; 568974</t>
+          <t>526796; 568948</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>832162; 889470</t>
+          <t>832977; 888581</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>212122; 228344</t>
+          <t>211452; 228584</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>294183; 312662</t>
+          <t>294837; 313028</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>512587; 537423</t>
+          <t>513618; 536751</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2958826; 3054492</t>
+          <t>2961758; 3072985</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2820047; 3129949</t>
+          <t>2825987; 3129795</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5820202; 6145157</t>
+          <t>5778210; 6145238</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A3_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P39A3_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,69; 95,09</t>
+          <t>85,21; 94,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,22; 96,15</t>
+          <t>88,83; 96,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,45; 94,57</t>
+          <t>88,94; 94,65</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,27; 95,47</t>
+          <t>88,71; 95,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,63; 92,83</t>
+          <t>88,01; 94,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,41; 93,02</t>
+          <t>89,79; 93,83</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,04; 93,86</t>
+          <t>87,77; 93,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,02; 92,12</t>
+          <t>87,55; 91,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,34; 92,55</t>
+          <t>88,56; 91,8</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>92,14; 97,86</t>
+          <t>89,63; 94,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,89; 91,52</t>
+          <t>87,84; 91,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,84; 95,63</t>
+          <t>89,3; 92,11</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,58; 93,09</t>
+          <t>87,28; 92,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,07; 93,56</t>
+          <t>89,82; 93,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,89; 92,77</t>
+          <t>89,42; 92,25</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>87,69; 92,87</t>
+          <t>87,77; 92,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,94; 98,22</t>
+          <t>88,81; 92,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90,49; 96,54</t>
+          <t>89,09; 92,29</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>84,28; 91,11</t>
+          <t>84,19; 90,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83,94; 89,12</t>
+          <t>83,3; 88,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85,3; 89,14</t>
+          <t>84,81; 89,12</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>90,85; 94,26</t>
+          <t>89,77; 91,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>82,87; 91,77</t>
+          <t>89,57; 91,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,62; 92,13</t>
+          <t>89,92; 91,27</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>329461</t>
+          <t>323271</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>258201</t>
+          <t>300627</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>587662</t>
+          <t>623898</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>309200; 343136</t>
+          <t>303533; 337797</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>245314; 267376</t>
+          <t>285751; 309885</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>565110; 604233</t>
+          <t>602914; 641661</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>364109</t>
+          <t>408821</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>387021</t>
+          <t>428475</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>751131</t>
+          <t>837295</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>347383; 375730</t>
+          <t>392794; 422572</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>213946; 455174</t>
+          <t>411662; 439737</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>569305; 822133</t>
+          <t>817591; 854366</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>475838</t>
+          <t>533301</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>475151</t>
+          <t>537057</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>950989</t>
+          <t>1070358</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>462457; 487513</t>
+          <t>514715; 545443</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>462533; 484052</t>
+          <t>523862; 548682</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>933537; 967004</t>
+          <t>1049196; 1087681</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>815520</t>
+          <t>611138</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>592970</t>
+          <t>638499</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1408489</t>
+          <t>1249637</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>792853; 842148</t>
+          <t>595204; 624645</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>579876; 603769</t>
+          <t>625585; 650105</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1381031; 1453828</t>
+          <t>1228945; 1267716</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>486031</t>
+          <t>518506</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>484381</t>
+          <t>534631</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>970412</t>
+          <t>1053136</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>472832; 496927</t>
+          <t>502281; 530452</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473978; 492321</t>
+          <t>524279; 544666</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>952813; 983347</t>
+          <t>1036498; 1069285</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>308557</t>
+          <t>340329</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>547409</t>
+          <t>369853</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>855966</t>
+          <t>710182</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>299197; 316869</t>
+          <t>330583; 348807</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>526796; 568948</t>
+          <t>360669; 377167</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>832977; 888581</t>
+          <t>697375; 722403</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>220859</t>
+          <t>242849</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>305229</t>
+          <t>331688</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>526088</t>
+          <t>574537</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>211452; 228584</t>
+          <t>232522; 250969</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>294837; 313028</t>
+          <t>320099; 341104</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>513618; 536751</t>
+          <t>560125; 588599</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>3000375</t>
+          <t>2978214</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3050363</t>
+          <t>3140829</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6050738</t>
+          <t>6119043</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2961758; 3072985</t>
+          <t>2942361; 3011350</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2825987; 3129795</t>
+          <t>3111738; 3166450</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5778210; 6145238</t>
+          <t>6071379; 6162176</t>
         </is>
       </c>
     </row>
